--- a/example/example-0002_dra_metadata.xlsx
+++ b/example/example-0002_dra_metadata.xlsx
@@ -1,17 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\sub2xml-dra-1.6.1\submission-excel2xml\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D11763-06C0-45D1-9EA8-135DBF028921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{45929CF0-44B2-436E-9881-1C2E579C9547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{18274612-E608-49F9-9BBD-C6D3797B9529}"/>
+    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{18274612-E608-49F9-9BBD-C6D3797B9529}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -421,7 +421,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="388" uniqueCount="319">
   <si>
     <t>Library Source</t>
   </si>
@@ -1410,11 +1410,15 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>2024-10-23 Bioinformation and DDBJ Center</t>
+    <t>2024-xx-yy Bioinformation and DDBJ Center</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>v3.1</t>
+    <t>v3.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -2215,7 +2219,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2AA6A301-AEBC-4D77-B71C-4D1BCE29DD0C}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$83</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I3000</xm:sqref>
         </x14:dataValidation>
@@ -29102,7 +29106,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H83"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -29483,8 +29487,8 @@
       <c r="C19" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D19" s="5" t="s">
-        <v>63</v>
+      <c r="D19" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -29500,7 +29504,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>153</v>
+        <v>63</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -29516,7 +29520,7 @@
         <v>57</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -29532,7 +29536,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -29548,7 +29552,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>115</v>
+        <v>152</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -29564,7 +29568,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>155</v>
+        <v>115</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -29580,7 +29584,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>302</v>
+        <v>155</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -29596,7 +29600,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>156</v>
+        <v>302</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -29612,7 +29616,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -29628,7 +29632,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -29644,7 +29648,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -29660,7 +29664,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>303</v>
+        <v>158</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -29674,7 +29678,7 @@
         <v>83</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>90</v>
+        <v>303</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -29688,7 +29692,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -29702,7 +29706,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -29716,7 +29720,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>159</v>
+        <v>121</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -29730,7 +29734,7 @@
         <v>111</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>304</v>
+        <v>159</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -29744,7 +29748,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -29758,7 +29762,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -29772,7 +29776,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>88</v>
+        <v>306</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -29784,7 +29788,7 @@
       <c r="B39" s="6"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -29796,7 +29800,7 @@
       <c r="B40" s="6"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>120</v>
+        <v>89</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -29804,212 +29808,217 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="D41" s="2" t="s">
-        <v>160</v>
+      <c r="D41" s="5" t="s">
+        <v>120</v>
       </c>
     </row>
     <row r="42" spans="1:8">
       <c r="D42" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="43" spans="1:8">
       <c r="D43" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="D44" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="D45" s="2" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8">
-      <c r="D45" s="5" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="46" spans="1:8">
       <c r="D46" s="5" t="s">
-        <v>122</v>
+        <v>93</v>
       </c>
     </row>
     <row r="47" spans="1:8">
       <c r="D47" s="5" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="D48" s="5" t="s">
         <v>123</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
-      <c r="D48" s="2" t="s">
-        <v>307</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="2" t="s">
-        <v>18</v>
+        <v>307</v>
       </c>
     </row>
     <row r="50" spans="4:4">
       <c r="D50" s="2" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
     </row>
     <row r="51" spans="4:4">
       <c r="D51" s="2" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="52" spans="4:4">
       <c r="D52" s="2" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="2" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>37</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="2" t="s">
-        <v>308</v>
+        <v>94</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="2" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="2" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="2" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="2" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="2" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" s="2" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" s="2" t="s">
-        <v>68</v>
+        <v>315</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" s="2" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="2" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="2" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="2" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" s="2" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" s="2" t="s">
-        <v>65</v>
+        <v>119</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" s="2" t="s">
-        <v>86</v>
+        <v>65</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="2" t="s">
         <v>80</v>
       </c>
     </row>

--- a/example/example-0002_dra_metadata.xlsx
+++ b/example/example-0002_dra_metadata.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml\example\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\github\submission-excel2xml-dra161\submission-excel2xml\example\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81D11763-06C0-45D1-9EA8-135DBF028921}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB41AB2F-CD4D-4E48-883F-22AD511A3287}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="0" showVerticalScroll="0" showSheetTabs="0" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="430" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{18274612-E608-49F9-9BBD-C6D3797B9529}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" tabRatio="858" xr2:uid="{18274612-E608-49F9-9BBD-C6D3797B9529}"/>
   </bookViews>
   <sheets>
     <sheet name="Readme" sheetId="9" r:id="rId1"/>
@@ -421,7 +420,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="318">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="330">
   <si>
     <t>Library Source</t>
   </si>
@@ -1410,11 +1409,59 @@
     <t>Sentosa SQ301</t>
   </si>
   <si>
-    <t>2024-10-23 Bioinformation and DDBJ Center</t>
+    <t>Illumina MiSeq i100</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>v3.1</t>
+    <t>Illumina MiSeq i100 Plus</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Illumina NovaSeq X Plus</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DNBSEQ-T1+</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>CycloneSEQ</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SURFSeq 5000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>SURFSeq Q</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Saluseq Nimbo</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Salus Pro</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Salus EVO</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>G-seq500</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>G4</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>v3.3</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>2026-02-24 Bioinformation and DDBJ Center</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -1896,12 +1943,12 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="2" t="s">
-        <v>316</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="2" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="66">
@@ -1953,7 +2000,7 @@
         <v>297</v>
       </c>
       <c r="B2" s="1">
-        <v>46023</v>
+        <v>46753</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>299</v>
@@ -2215,7 +2262,7 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2AA6A301-AEBC-4D77-B71C-4D1BCE29DD0C}">
           <x14:formula1>
-            <xm:f>Admin!$D$2:$D$82</xm:f>
+            <xm:f>Admin!$D$2:$D$94</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I3000</xm:sqref>
         </x14:dataValidation>
@@ -29102,7 +29149,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:H82"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="13.2"/>
   <cols>
     <col min="1" max="1" width="32.33203125" style="2" bestFit="1" customWidth="1"/>
@@ -29435,8 +29482,8 @@
       <c r="C16" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="5" t="s">
-        <v>163</v>
+      <c r="D16" s="2" t="s">
+        <v>316</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
@@ -29451,8 +29498,8 @@
       <c r="C17" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D17" s="5" t="s">
-        <v>114</v>
+      <c r="D17" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
@@ -29468,7 +29515,7 @@
         <v>51</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>301</v>
+        <v>163</v>
       </c>
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
@@ -29484,7 +29531,7 @@
         <v>54</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>63</v>
+        <v>114</v>
       </c>
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
@@ -29500,7 +29547,7 @@
         <v>55</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>153</v>
+        <v>301</v>
       </c>
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
@@ -29515,8 +29562,8 @@
       <c r="C21" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>151</v>
+      <c r="D21" s="2" t="s">
+        <v>318</v>
       </c>
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
@@ -29532,7 +29579,7 @@
         <v>59</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>152</v>
+        <v>63</v>
       </c>
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
@@ -29548,7 +29595,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
@@ -29564,7 +29611,7 @@
         <v>67</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
@@ -29580,7 +29627,7 @@
         <v>70</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>302</v>
+        <v>152</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
@@ -29596,7 +29643,7 @@
         <v>73</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
@@ -29612,7 +29659,7 @@
         <v>75</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
@@ -29628,7 +29675,7 @@
         <v>78</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>154</v>
+        <v>302</v>
       </c>
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
@@ -29644,7 +29691,7 @@
         <v>146</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
@@ -29660,7 +29707,7 @@
         <v>81</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>303</v>
+        <v>157</v>
       </c>
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
@@ -29673,8 +29720,8 @@
       <c r="C31" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="D31" s="5" t="s">
-        <v>90</v>
+      <c r="D31" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
@@ -29688,7 +29735,7 @@
         <v>150</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>91</v>
+        <v>154</v>
       </c>
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
@@ -29702,7 +29749,7 @@
         <v>85</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>121</v>
+        <v>158</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
@@ -29716,7 +29763,7 @@
         <v>87</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>159</v>
+        <v>303</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
@@ -29729,8 +29776,8 @@
       <c r="C35" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>304</v>
+      <c r="D35" s="2" t="s">
+        <v>320</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
@@ -29744,7 +29791,7 @@
         <v>110</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>305</v>
+        <v>90</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
@@ -29758,7 +29805,7 @@
         <v>147</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>306</v>
+        <v>91</v>
       </c>
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
@@ -29772,7 +29819,7 @@
         <v>38</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
@@ -29784,7 +29831,7 @@
       <c r="B39" s="6"/>
       <c r="C39" s="5"/>
       <c r="D39" s="5" t="s">
-        <v>89</v>
+        <v>159</v>
       </c>
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
@@ -29796,7 +29843,7 @@
       <c r="B40" s="6"/>
       <c r="C40" s="5"/>
       <c r="D40" s="5" t="s">
-        <v>120</v>
+        <v>304</v>
       </c>
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
@@ -29804,212 +29851,272 @@
       <c r="H40" s="5"/>
     </row>
     <row r="41" spans="1:8">
-      <c r="D41" s="2" t="s">
-        <v>160</v>
+      <c r="D41" s="5" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:8">
-      <c r="D42" s="2" t="s">
-        <v>161</v>
+      <c r="D42" s="5" t="s">
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:8">
-      <c r="D43" s="2" t="s">
-        <v>162</v>
+      <c r="D43" s="5" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="44" spans="1:8">
-      <c r="D44" s="2" t="s">
-        <v>92</v>
+      <c r="D44" s="5" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="45" spans="1:8">
       <c r="D45" s="5" t="s">
-        <v>93</v>
+        <v>120</v>
       </c>
     </row>
     <row r="46" spans="1:8">
-      <c r="D46" s="5" t="s">
-        <v>122</v>
+      <c r="D46" s="2" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:8">
-      <c r="D47" s="5" t="s">
-        <v>123</v>
+      <c r="D47" s="2" t="s">
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:8">
       <c r="D48" s="2" t="s">
-        <v>307</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="4:4">
       <c r="D49" s="2" t="s">
-        <v>18</v>
+        <v>92</v>
       </c>
     </row>
     <row r="50" spans="4:4">
-      <c r="D50" s="2" t="s">
-        <v>23</v>
+      <c r="D50" s="5" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="51" spans="4:4">
-      <c r="D51" s="2" t="s">
-        <v>27</v>
+      <c r="D51" s="5" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="52" spans="4:4">
-      <c r="D52" s="2" t="s">
-        <v>31</v>
+      <c r="D52" s="5" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="53" spans="4:4">
       <c r="D53" s="2" t="s">
-        <v>35</v>
+        <v>307</v>
       </c>
     </row>
     <row r="54" spans="4:4">
       <c r="D54" s="2" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
     </row>
     <row r="55" spans="4:4">
       <c r="D55" s="2" t="s">
-        <v>100</v>
+        <v>23</v>
       </c>
     </row>
     <row r="56" spans="4:4">
       <c r="D56" s="2" t="s">
-        <v>99</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57" spans="4:4">
       <c r="D57" s="2" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
     </row>
     <row r="58" spans="4:4">
       <c r="D58" s="2" t="s">
-        <v>97</v>
+        <v>35</v>
       </c>
     </row>
     <row r="59" spans="4:4">
       <c r="D59" s="2" t="s">
-        <v>96</v>
+        <v>37</v>
       </c>
     </row>
     <row r="60" spans="4:4">
       <c r="D60" s="2" t="s">
-        <v>95</v>
+        <v>100</v>
       </c>
     </row>
     <row r="61" spans="4:4">
       <c r="D61" s="2" t="s">
-        <v>94</v>
+        <v>99</v>
       </c>
     </row>
     <row r="62" spans="4:4">
       <c r="D62" s="2" t="s">
-        <v>308</v>
+        <v>98</v>
       </c>
     </row>
     <row r="63" spans="4:4">
       <c r="D63" s="2" t="s">
-        <v>309</v>
+        <v>97</v>
       </c>
     </row>
     <row r="64" spans="4:4">
       <c r="D64" s="2" t="s">
-        <v>310</v>
+        <v>96</v>
       </c>
     </row>
     <row r="65" spans="4:4">
       <c r="D65" s="2" t="s">
-        <v>311</v>
+        <v>95</v>
       </c>
     </row>
     <row r="66" spans="4:4">
       <c r="D66" s="2" t="s">
-        <v>312</v>
+        <v>94</v>
       </c>
     </row>
     <row r="67" spans="4:4">
       <c r="D67" s="2" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
     </row>
     <row r="68" spans="4:4">
       <c r="D68" s="2" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
     </row>
     <row r="69" spans="4:4">
       <c r="D69" s="2" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
     </row>
     <row r="70" spans="4:4">
       <c r="D70" s="2" t="s">
-        <v>68</v>
+        <v>321</v>
       </c>
     </row>
     <row r="71" spans="4:4">
       <c r="D71" s="2" t="s">
-        <v>71</v>
+        <v>322</v>
       </c>
     </row>
     <row r="72" spans="4:4">
       <c r="D72" s="2" t="s">
-        <v>74</v>
+        <v>311</v>
       </c>
     </row>
     <row r="73" spans="4:4">
       <c r="D73" s="2" t="s">
-        <v>76</v>
+        <v>312</v>
       </c>
     </row>
     <row r="74" spans="4:4">
       <c r="D74" s="2" t="s">
-        <v>79</v>
+        <v>313</v>
       </c>
     </row>
     <row r="75" spans="4:4">
       <c r="D75" s="2" t="s">
-        <v>82</v>
+        <v>314</v>
       </c>
     </row>
     <row r="76" spans="4:4">
       <c r="D76" s="2" t="s">
-        <v>84</v>
+        <v>315</v>
       </c>
     </row>
     <row r="77" spans="4:4">
       <c r="D77" s="2" t="s">
-        <v>117</v>
+        <v>323</v>
       </c>
     </row>
     <row r="78" spans="4:4">
       <c r="D78" s="2" t="s">
-        <v>118</v>
+        <v>324</v>
       </c>
     </row>
     <row r="79" spans="4:4">
       <c r="D79" s="2" t="s">
-        <v>119</v>
+        <v>325</v>
       </c>
     </row>
     <row r="80" spans="4:4">
       <c r="D80" s="2" t="s">
-        <v>65</v>
+        <v>326</v>
       </c>
     </row>
     <row r="81" spans="4:4">
       <c r="D81" s="2" t="s">
-        <v>86</v>
+        <v>327</v>
       </c>
     </row>
     <row r="82" spans="4:4">
       <c r="D82" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="83" spans="4:4">
+      <c r="D83" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="4:4">
+      <c r="D84" s="2" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="85" spans="4:4">
+      <c r="D85" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="86" spans="4:4">
+      <c r="D86" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="4:4">
+      <c r="D87" s="2" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="88" spans="4:4">
+      <c r="D88" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="89" spans="4:4">
+      <c r="D89" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="90" spans="4:4">
+      <c r="D90" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="91" spans="4:4">
+      <c r="D91" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="92" spans="4:4">
+      <c r="D92" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="93" spans="4:4">
+      <c r="D93" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="4:4">
+      <c r="D94" s="2" t="s">
         <v>80</v>
       </c>
     </row>
